--- a/output/pdf_financials_xlsx/SDE.xlsx
+++ b/output/pdf_financials_xlsx/SDE.xlsx
@@ -6657,7 +6657,7 @@
         <v>2.503777</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.544136</v>
+        <v>7.712454</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>3.850302</v>
@@ -8207,19 +8207,19 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>3.11854</v>
+        <v>0.8833839999999999</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>0.256439</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.114908</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-2.446692</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>4.851796</v>
+        <v>3.350258</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>0.054136</v>
@@ -8228,7 +8228,7 @@
         <v>0</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.133939</v>
       </c>
       <c r="L118" s="3" t="n">
         <v>-0.218727</v>
@@ -60448,7 +60448,11 @@
           <t>Exploration and evaluation expenditures (note 5)</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr">
         <is>
           <t>-</t>
@@ -67420,7 +67424,11 @@
           <t>Exploration and evaluation expenditures (note 7)</t>
         </is>
       </c>
-      <c r="D558" t="inlineStr"/>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E558" t="inlineStr">
         <is>
           <t>-</t>
@@ -69852,7 +69860,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D581" t="inlineStr"/>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E581" t="inlineStr">
         <is>
           <t>-</t>
@@ -72582,7 +72594,11 @@
           <t>Recovery of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D607" t="inlineStr"/>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E607" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SDE.xlsx
+++ b/output/pdf_financials_xlsx/SDE.xlsx
@@ -2955,34 +2955,34 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.55065</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>4.620125</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>4.620125</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.141192</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.008989</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.252188</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.92864</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.166218</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.6028480000000001</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>5.785294</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0.974813</v>
@@ -3077,34 +3077,34 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.55065</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>4.620125</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>4.620125</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.141192</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.008989</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.252188</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.92864</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.166218</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.6028480000000001</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>5.785294</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>0.974813</v>
@@ -3809,13 +3809,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.622962</v>
+        <v>0.072312</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.360891</v>
+        <v>0.740766</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>5.360891</v>
+        <v>0.740766</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -8607,22 +8607,22 @@
         <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.003392</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.007860000000000001</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.009087</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.009605000000000001</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.009482000000000001</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>0</v>
+        <v>-0.009811</v>
       </c>
     </row>
     <row r="125">
@@ -8668,22 +8668,22 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.003392</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.007860000000000001</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.009087</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.009605000000000001</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.009482000000000001</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>0</v>
+        <v>-0.009811</v>
       </c>
     </row>
     <row r="126">
@@ -33644,7 +33644,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E235" s="5" t="n">
@@ -43072,7 +43072,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -44676,7 +44676,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -46178,7 +46178,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -50056,7 +50056,11 @@
           <t>Lease payments [8]</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
@@ -53870,7 +53874,11 @@
           <t>Lease payments [9]</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SDE.xlsx
+++ b/output/pdf_financials_xlsx/SDE.xlsx
@@ -1533,15 +1533,11 @@
       <c r="F16" s="3" t="n">
         <v>-0.448604</v>
       </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G16" s="3" t="n">
+        <v>-2.218776</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>-5.816364</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-0.681319</v>
@@ -1878,32 +1874,28 @@
         <v>-5.832772</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-9.094555</v>
+        <v>-0.299616</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-2.799469</v>
+        <v>-3.630372</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-0.119247</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-0.448604</v>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.641822</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>-2.218776</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>-5.816364</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-0.681319</v>
+        <v>-0.500966</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-0.391324</v>
+        <v>-0.650593</v>
       </c>
       <c r="K20" s="1" t="inlineStr">
         <is>
@@ -1961,10 +1953,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-8.794938999999999</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>-1.549584</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -2130,15 +2122,11 @@
       <c r="F23" s="3" t="n">
         <v>-0.448604</v>
       </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G23" s="3" t="n">
+        <v>-2.218776</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>-5.816364</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-0.681319</v>
@@ -2146,10 +2134,8 @@
       <c r="J23" s="3" t="n">
         <v>-0.391324</v>
       </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K23" s="3" t="n">
+        <v>-2.35697</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>-3.156096</v>
@@ -2381,15 +2367,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G26" s="3" t="n">
+        <v>110.9388</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>116.32728</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -2468,15 +2450,11 @@
       <c r="F27" s="3" t="n">
         <v>-0.448604</v>
       </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G27" s="3" t="n">
+        <v>-2.218776</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>-5.816364</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.681319</v>
@@ -2630,15 +2608,11 @@
       <c r="F29" s="3" t="n">
         <v>0.223139</v>
       </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G29" s="3" t="n">
+        <v>-1.33414</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>-5.809952</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.673912</v>
@@ -2713,15 +2687,11 @@
       <c r="F30" s="3" t="n">
         <v>10.83699319443102</v>
       </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G30" s="3" t="n">
+        <v>-63.99990022052224</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>-9013.267142413901</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>-1895.567056705671</v>
@@ -2796,15 +2766,11 @@
       <c r="F31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -2879,15 +2845,11 @@
       <c r="F32" s="3" t="n">
         <v>-21.78695116046291</v>
       </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G32" s="3" t="n">
+        <v>-106.4366877626707</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>-9023.214396524976</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>-1916.401327632763</v>
@@ -7039,37 +7001,31 @@
         <v>-5.832772</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>-9.094555</v>
+        <v>-0.299616</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>-2.799469</v>
+        <v>-3.630372</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-0.119247</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>-0.448604</v>
-      </c>
-      <c r="G99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.641822</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>-2.218776</v>
+      </c>
+      <c r="H99" s="3" t="n">
+        <v>-5.816364</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>-0.681319</v>
+        <v>-0.500966</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>-0.391324</v>
-      </c>
-      <c r="K99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.650593</v>
+      </c>
+      <c r="K99" s="3" t="n">
+        <v>-2.35697</v>
       </c>
       <c r="L99" s="3" t="n">
         <v>-3.156096</v>
@@ -7502,7 +7458,7 @@
         <v>-0.103261</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0</v>
+        <v>0.6026860000000001</v>
       </c>
       <c r="N106" s="3" t="n">
         <v>0</v>
@@ -49442,7 +49398,11 @@
           <t>Deferred income tax expense [12]</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr">
         <is>
           <t>-</t>
@@ -53046,7 +53006,11 @@
           <t>Deferred income tax expense [13]</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr"/>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E421" t="inlineStr">
         <is>
           <t>-</t>
@@ -55952,7 +55916,11 @@
           <t>Deferred income tax expense [14]</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
           <t>-</t>
@@ -57312,7 +57280,11 @@
           <t>Deferred income tax expense (recovery) [14]</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
@@ -58778,7 +58750,11 @@
           <t>Change in non-cash operating working capital [15]</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
           <t>-</t>
@@ -61844,7 +61820,11 @@
           <t>Loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
           <t>-</t>
@@ -72176,7 +72156,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D603" t="inlineStr"/>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E603" t="inlineStr">
         <is>
           <t>-</t>
@@ -79500,7 +79484,11 @@
           <t>LOSS FROM CONTINUING OPERATIONS</t>
         </is>
       </c>
-      <c r="D673" t="inlineStr"/>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E673" t="inlineStr">
         <is>
           <t>-</t>
@@ -83672,7 +83660,11 @@
           <t>LOSS FROM CONTINUING OPERATIONS</t>
         </is>
       </c>
-      <c r="D713" t="inlineStr"/>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E713" t="inlineStr">
         <is>
           <t>-</t>
@@ -85442,7 +85434,11 @@
           <t>LOSS FROM CONTINUING OPERATIONS</t>
         </is>
       </c>
-      <c r="D730" t="inlineStr"/>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E730" t="inlineStr">
         <is>
           <t>-</t>
@@ -85544,7 +85540,11 @@
           <t>LOSS FROM DISCONTINUED OPERATIONS (note 15)</t>
         </is>
       </c>
-      <c r="D731" t="inlineStr"/>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E731" t="inlineStr">
         <is>
           <t>-</t>
@@ -90144,7 +90144,11 @@
           <t>LOSS FROM DISCONTINUED OPERATIONS (note 13)</t>
         </is>
       </c>
-      <c r="D775" t="inlineStr"/>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E775" t="inlineStr">
         <is>
           <t>-</t>
